--- a/artfynd/S 2823-2025 artfynd.xlsx
+++ b/artfynd/S 2823-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY122"/>
+  <dimension ref="A1:AZ122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105197201</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/161074</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/161075</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1116,6 +1136,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/161076</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1227,6 +1252,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/161077</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1338,6 +1368,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/161078</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1449,6 +1484,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/161079</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1560,6 +1600,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/161080</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1671,6 +1716,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/161081</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1782,6 +1832,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/161082</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1893,6 +1948,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/161083</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2004,6 +2064,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/161084</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2105,6 +2170,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107448320</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2206,6 +2276,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107448388</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2317,6 +2392,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/179503</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2428,6 +2508,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/179504</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2539,6 +2624,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/179505</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2650,6 +2740,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/179506</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2761,6 +2856,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/179507</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2862,6 +2962,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104320729</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2973,6 +3078,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/194312</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3084,6 +3194,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/194313</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3195,6 +3310,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/194314</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3306,6 +3426,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/194315</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3417,6 +3542,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/194316</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3528,6 +3658,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/194317</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3629,6 +3764,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104320730</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3730,6 +3870,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107448318</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3831,6 +3976,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107448390</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3942,6 +4092,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/151908</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4053,6 +4208,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/151909</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4164,6 +4324,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/151910</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4264,6 +4429,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16636348</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4365,6 +4535,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107448337</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4476,6 +4651,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/910868</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4577,6 +4757,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107448403</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4678,6 +4863,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107448326</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4779,6 +4969,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107448405</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4880,6 +5075,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107448396</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4991,6 +5191,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1161495</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5092,6 +5297,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107448321</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5193,6 +5403,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107448401</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5309,6 +5524,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1356936</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5425,6 +5645,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1356937</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5541,6 +5766,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1356938</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5646,6 +5876,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104040825</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5747,6 +5982,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104320472</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5848,6 +6088,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104320492</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5949,6 +6194,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104320651</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6050,6 +6300,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107448325</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6151,6 +6406,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107448333</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6252,6 +6512,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107448406</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6363,6 +6628,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1426948</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6463,6 +6733,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16636345</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6564,6 +6839,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107448331</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6665,6 +6945,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107448393</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6776,6 +7061,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1756507</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6887,6 +7177,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1756508</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6988,6 +7283,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104320475</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7089,6 +7389,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107448329</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7190,6 +7495,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107448404</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7301,6 +7611,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1798353</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7412,6 +7727,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1798354</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7523,6 +7843,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1798355</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7624,6 +7949,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107448332</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7725,6 +8055,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107448330</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7826,6 +8161,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107448335</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7927,6 +8267,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107448400</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8038,6 +8383,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1216757</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8149,6 +8499,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1341894</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8265,6 +8620,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1341895</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8381,6 +8741,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1341896</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8482,6 +8847,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107448327</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8583,6 +8953,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107448334</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8684,6 +9059,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107448395</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8785,6 +9165,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104320731</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8896,6 +9281,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1751534</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9007,6 +9397,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1751535</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9108,6 +9503,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107448328</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9209,6 +9609,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107448398</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9307,6 +9712,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110337215</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9409,6 +9819,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110337202</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9520,6 +9935,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6588204</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9621,6 +10041,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107448324</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9732,6 +10157,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6624106</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9843,6 +10273,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6624107</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9954,6 +10389,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6624108</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10065,6 +10505,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6624109</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10176,6 +10621,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6624110</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10277,6 +10727,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107448319</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10378,6 +10833,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107448407</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10479,6 +10939,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104320480</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10580,6 +11045,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104320482</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10681,6 +11151,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104320703</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10792,6 +11267,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6625548</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10903,6 +11383,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6625549</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11011,6 +11496,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16636346</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11112,6 +11602,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104320478</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11213,6 +11708,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104320481</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11314,6 +11814,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104320483</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11415,6 +11920,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104320485</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11516,6 +12026,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104320486</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11617,6 +12132,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104320487</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11718,6 +12238,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104320488</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11819,6 +12344,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104320517</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11920,6 +12450,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104320704</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12021,6 +12556,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104320705</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12122,6 +12662,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104320727</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12223,6 +12768,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107448323</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12324,6 +12874,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107448408</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12435,6 +12990,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6632250</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12551,6 +13111,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6632251</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12662,6 +13227,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6632252</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12773,6 +13343,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6632253</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12874,6 +13449,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104320473</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12975,6 +13555,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104320474</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -13076,6 +13661,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104320476</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -13177,6 +13767,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104320493</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -13278,6 +13873,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104320735</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -13386,6 +13986,11 @@
       <c r="AY121" t="inlineStr">
         <is>
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106216015</t>
         </is>
       </c>
     </row>
@@ -13489,8 +14094,136 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16636344</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>